--- a/schedule_output.xlsx
+++ b/schedule_output.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schedule" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hour Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Warnings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strike List" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,7 +141,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -214,6 +215,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6372,4 +6382,838 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Missing Requirements</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>Maria Gonzalez</t>
+        </is>
+      </c>
+      <c r="B2" s="18" t="inlineStr">
+        <is>
+          <t>maria_t_gonzalez@brown.edu</t>
+        </is>
+      </c>
+      <c r="C2" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D2" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Daniel Koo</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>daniel_koo@brown.edu</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D3" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="26" t="inlineStr">
+        <is>
+          <t>Eric Wang</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>eric_wang7@brown.edu</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY NIGHT, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Nadjasmine Rene</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>nadjasmine_rene@brown.edu</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26" t="inlineStr">
+        <is>
+          <t>Raphel Awa</t>
+        </is>
+      </c>
+      <c r="B6" s="18" t="inlineStr">
+        <is>
+          <t>raphel_awa@brown.edu</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM, WEEKDAY NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Adrian Lin</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>adrian_lin@brown.edu</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D7" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>Tae-Jin Shah</t>
+        </is>
+      </c>
+      <c r="B8" s="18" t="inlineStr">
+        <is>
+          <t>tae-jin_shah@brown.edu</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Riley Frey</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>riley_frey@brown.edu</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM, WEEKDAY NIGHT, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>Ella Therese Olea</t>
+        </is>
+      </c>
+      <c r="B10" s="18" t="inlineStr">
+        <is>
+          <t>ella_olea@brown.edu</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Janet Weng</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>linghan_weng@brown.edu</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D11" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM, WEEKDAY NIGHT, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>Ethan Aguiar</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="inlineStr">
+        <is>
+          <t>ethan_aguiar@brown.edu</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Ogechukwu Iwuchukwu</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>ogechukwu_iwuchukwu@brown.edu</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D13" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>Jolie Leibner</t>
+        </is>
+      </c>
+      <c r="B14" s="18" t="inlineStr">
+        <is>
+          <t>jolie_leibner@brown.edu</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Matteo Sredzinski</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>matteo_sredzinski@brown.edu</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="inlineStr">
+        <is>
+          <t>Lisa Miyazaki</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>lisa_miyazaki@brown.edu</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKDAY PM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Mateen Markzar</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>mateen_markzar@brown.edu</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D17" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKDAY PM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="inlineStr">
+        <is>
+          <t>Catherine Dunn</t>
+        </is>
+      </c>
+      <c r="B18" s="18" t="inlineStr">
+        <is>
+          <t>catherine_dunn@brown.edu</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Hannah Moon</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>hannah_moon@brown.edu</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D19" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>Isabelle Gary</t>
+        </is>
+      </c>
+      <c r="B20" s="18" t="inlineStr">
+        <is>
+          <t>isabelle_gary@brown.edu</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>WEEKEND DAY, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Andy Le</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>huy_le@brown.edu</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D21" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26" t="inlineStr">
+        <is>
+          <t>Nikhil Sonthalia</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>nikhil_sonthalia@brown.edu</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>Amber Wang</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>amber_wang@brown.edu</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKEND DAY, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26" t="inlineStr">
+        <is>
+          <t>Kelley Tu</t>
+        </is>
+      </c>
+      <c r="B24" s="18" t="inlineStr">
+        <is>
+          <t>kelley_tu@brown.edu</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D24" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>MATTHEW HARM</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>matthew_harm@brown.edu</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D25" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY PM, WEEKDAY NIGHT, WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="26" t="inlineStr">
+        <is>
+          <t>Kassra Ehsan</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>kassra_ehsan@brown.edu</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>Olivia Schmidt</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>olivia_schmidt@brown.edu</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D27" s="28" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
+          <t>Anthony Kharrat</t>
+        </is>
+      </c>
+      <c r="B28" s="18" t="inlineStr">
+        <is>
+          <t>anthony_kharrat@brown.edu</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D28" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM, WEEKDAY NIGHT, WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Ella Hankins</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>ella_hankins@brown.edu</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D29" s="28" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="26" t="inlineStr">
+        <is>
+          <t>Evan MacLure</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>evan_maclure@brown.edu</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D30" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Ruiyang Zhu</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>ruiyang_zhu@brown.edu</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D31" s="28" t="inlineStr">
+        <is>
+          <t>WEEKEND DAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="26" t="inlineStr">
+        <is>
+          <t>Barron Clancy</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>john_b_clancy@brown.edu</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D32" s="27" t="inlineStr">
+        <is>
+          <t>WEEKDAY NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Lachlan Kirby</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>lachlan_kirby@brown.edu</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D33" s="28" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="26" t="inlineStr">
+        <is>
+          <t>Melanie Ho</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>melanie_ho@brown.edu</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D34" s="27" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Sonia Sheth</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>sonia_sheth@brown.edu</t>
+        </is>
+      </c>
+      <c r="C35" s="7" t="inlineStr">
+        <is>
+          <t>Auth</t>
+        </is>
+      </c>
+      <c r="D35" s="28" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="26" t="inlineStr">
+        <is>
+          <t>Lukas Strelecky</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>lukas_strelecky@brown.edu</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>EVDT</t>
+        </is>
+      </c>
+      <c r="D36" s="27" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Aryan Narayan</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>aryan_narayan@brown.edu</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr">
+        <is>
+          <t>EMT</t>
+        </is>
+      </c>
+      <c r="D37" s="28" t="inlineStr">
+        <is>
+          <t>WEEKEND NIGHT</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>